--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/27.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/27.xlsx
@@ -426,13 +426,13 @@
         <v>-12.12039984597261</v>
       </c>
       <c r="E2">
-        <v>-14.29581940272395</v>
+        <v>-16.10850414935828</v>
       </c>
       <c r="F2">
-        <v>-1.260303164888759</v>
+        <v>-0.8400831502248067</v>
       </c>
       <c r="G2">
-        <v>-8.768931137997845</v>
+        <v>-9.818314484127104</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.28752069542132</v>
       </c>
       <c r="E3">
-        <v>-15.2565895051393</v>
+        <v>-16.95051954939649</v>
       </c>
       <c r="F3">
-        <v>-1.541087408109083</v>
+        <v>-0.7579554924416526</v>
       </c>
       <c r="G3">
-        <v>-8.36776916118558</v>
+        <v>-9.646960647014426</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-12.45431582314403</v>
       </c>
       <c r="E4">
-        <v>-15.12978770445053</v>
+        <v>-17.23554170343927</v>
       </c>
       <c r="F4">
-        <v>-1.290237049356322</v>
+        <v>-0.4216764318055821</v>
       </c>
       <c r="G4">
-        <v>-8.434724944717338</v>
+        <v>-10.14023193236583</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.56578626407253</v>
       </c>
       <c r="E5">
-        <v>-16.8101277982107</v>
+        <v>-18.38301173224286</v>
       </c>
       <c r="F5">
-        <v>-1.662585711812492</v>
+        <v>-0.5835369372103971</v>
       </c>
       <c r="G5">
-        <v>-8.309516801876564</v>
+        <v>-9.850201658761364</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.59839572493358</v>
       </c>
       <c r="E6">
-        <v>-16.91345398964371</v>
+        <v>-18.91728562414182</v>
       </c>
       <c r="F6">
-        <v>-1.63407827601255</v>
+        <v>-0.8739468096512506</v>
       </c>
       <c r="G6">
-        <v>-8.367679776456018</v>
+        <v>-10.12912836262712</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-12.52986955862509</v>
       </c>
       <c r="E7">
-        <v>-16.72290938882297</v>
+        <v>-19.33951601214299</v>
       </c>
       <c r="F7">
-        <v>-1.568977710193939</v>
+        <v>-0.5738682328849213</v>
       </c>
       <c r="G7">
-        <v>-8.018268247513641</v>
+        <v>-9.311791084981994</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-12.33039895408186</v>
       </c>
       <c r="E8">
-        <v>-17.94779820926169</v>
+        <v>-19.97491072863323</v>
       </c>
       <c r="F8">
-        <v>-1.497183935760709</v>
+        <v>-0.8573463268991485</v>
       </c>
       <c r="G8">
-        <v>-7.537990853403874</v>
+        <v>-9.578382696168424</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-12.00178008097733</v>
       </c>
       <c r="E9">
-        <v>-18.37221132173456</v>
+        <v>-20.13570325522358</v>
       </c>
       <c r="F9">
-        <v>-1.729549275919998</v>
+        <v>-0.2750388341620136</v>
       </c>
       <c r="G9">
-        <v>-8.09109031774099</v>
+        <v>-9.534137255036065</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-11.53959864981031</v>
       </c>
       <c r="E10">
-        <v>-18.79965851179258</v>
+        <v>-20.74293539186011</v>
       </c>
       <c r="F10">
-        <v>-1.391499994144145</v>
+        <v>-1.033786098593235</v>
       </c>
       <c r="G10">
-        <v>-7.612497991310711</v>
+        <v>-9.611647057747021</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-10.95750829356738</v>
       </c>
       <c r="E11">
-        <v>-19.26771705675138</v>
+        <v>-22.25220332303252</v>
       </c>
       <c r="F11">
-        <v>-1.397925640087661</v>
+        <v>-0.1049327596297323</v>
       </c>
       <c r="G11">
-        <v>-7.114492625838147</v>
+        <v>-8.42980878459152</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-10.28994234122136</v>
       </c>
       <c r="E12">
-        <v>-21.37540018566738</v>
+        <v>-23.04368095314513</v>
       </c>
       <c r="F12">
-        <v>-1.039072739357901</v>
+        <v>-0.2671792842442519</v>
       </c>
       <c r="G12">
-        <v>-7.0461133077245</v>
+        <v>-8.258299351838499</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.563250883510049</v>
       </c>
       <c r="E13">
-        <v>-21.12314606954412</v>
+        <v>-22.94155933579815</v>
       </c>
       <c r="F13">
-        <v>-0.701267825965874</v>
+        <v>-0.2822563993426057</v>
       </c>
       <c r="G13">
-        <v>-6.20595643967718</v>
+        <v>-7.550822527914089</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-8.839613111525379</v>
       </c>
       <c r="E14">
-        <v>-21.49916338029702</v>
+        <v>-24.12038904710487</v>
       </c>
       <c r="F14">
-        <v>-0.9313303047453807</v>
+        <v>0.3839199794583679</v>
       </c>
       <c r="G14">
-        <v>-6.779299889986938</v>
+        <v>-7.28658802515162</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.166062808324597</v>
       </c>
       <c r="E15">
-        <v>-24.6147987823143</v>
+        <v>-24.75493241048166</v>
       </c>
       <c r="F15">
-        <v>-0.1120799135810865</v>
+        <v>0.553787484178643</v>
       </c>
       <c r="G15">
-        <v>-6.090891808368731</v>
+        <v>-7.479563035181276</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-7.589694467713452</v>
       </c>
       <c r="E16">
-        <v>-24.51898532926001</v>
+        <v>-25.9547380133919</v>
       </c>
       <c r="F16">
-        <v>-0.1171710596386922</v>
+        <v>0.82474314816475</v>
       </c>
       <c r="G16">
-        <v>-5.124298585085565</v>
+        <v>-7.037158282040772</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-7.160465839963465</v>
       </c>
       <c r="E17">
-        <v>-24.30764597579604</v>
+        <v>-27.18041931678196</v>
       </c>
       <c r="F17">
-        <v>0.2424795588999635</v>
+        <v>1.052446436581084</v>
       </c>
       <c r="G17">
-        <v>-5.028594024090775</v>
+        <v>-6.535527869202705</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-6.891849972372495</v>
       </c>
       <c r="E18">
-        <v>-24.89970772450688</v>
+        <v>-27.63376937816385</v>
       </c>
       <c r="F18">
-        <v>1.016927699083847</v>
+        <v>1.380532943603467</v>
       </c>
       <c r="G18">
-        <v>-5.037598707957592</v>
+        <v>-6.585659460303889</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-6.807455860423586</v>
       </c>
       <c r="E19">
-        <v>-26.47809828293236</v>
+        <v>-28.2730721677227</v>
       </c>
       <c r="F19">
-        <v>1.157251480383277</v>
+        <v>1.508275480789179</v>
       </c>
       <c r="G19">
-        <v>-4.825958842177525</v>
+        <v>-5.71910430212642</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-6.898360157524999</v>
       </c>
       <c r="E20">
-        <v>-27.56929296524264</v>
+        <v>-28.83112507663594</v>
       </c>
       <c r="F20">
-        <v>1.13066585695783</v>
+        <v>2.011936115569723</v>
       </c>
       <c r="G20">
-        <v>-5.060709626367244</v>
+        <v>-5.848715470534426</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-7.139767421744406</v>
       </c>
       <c r="E21">
-        <v>-27.73319202500225</v>
+        <v>-28.94911446690579</v>
       </c>
       <c r="F21">
-        <v>1.54036312050402</v>
+        <v>2.31973093469313</v>
       </c>
       <c r="G21">
-        <v>-4.631424565198871</v>
+        <v>-5.288935325299061</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-7.509712214788897</v>
       </c>
       <c r="E22">
-        <v>-27.67666761243851</v>
+        <v>-29.75916789739786</v>
       </c>
       <c r="F22">
-        <v>1.876932109731071</v>
+        <v>2.441085102468452</v>
       </c>
       <c r="G22">
-        <v>-4.847530356911416</v>
+        <v>-5.543075974712292</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-7.955920013462521</v>
       </c>
       <c r="E23">
-        <v>-28.98579510636792</v>
+        <v>-30.19055033136854</v>
       </c>
       <c r="F23">
-        <v>1.976960787088722</v>
+        <v>2.460241927025593</v>
       </c>
       <c r="G23">
-        <v>-4.530307262247372</v>
+        <v>-5.469601727013707</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.441630943863141</v>
       </c>
       <c r="E24">
-        <v>-28.7583072145926</v>
+        <v>-31.11353258242689</v>
       </c>
       <c r="F24">
-        <v>2.214205211250501</v>
+        <v>2.524831390156676</v>
       </c>
       <c r="G24">
-        <v>-4.666016455538716</v>
+        <v>-5.656349600883995</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.917661643280811</v>
       </c>
       <c r="E25">
-        <v>-29.50416499755194</v>
+        <v>-30.93093771772661</v>
       </c>
       <c r="F25">
-        <v>2.061762414848114</v>
+        <v>2.192815108175412</v>
       </c>
       <c r="G25">
-        <v>-4.461077133930133</v>
+        <v>-4.875971253639294</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-9.333048421244628</v>
       </c>
       <c r="E26">
-        <v>-28.44026342808589</v>
+        <v>-31.20670367089771</v>
       </c>
       <c r="F26">
-        <v>1.534473428270116</v>
+        <v>2.303410440123174</v>
       </c>
       <c r="G26">
-        <v>-4.747995494727689</v>
+        <v>-4.414855297110829</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-9.654047291284352</v>
       </c>
       <c r="E27">
-        <v>-29.42347664768327</v>
+        <v>-31.47015217476794</v>
       </c>
       <c r="F27">
-        <v>1.971556518152858</v>
+        <v>2.239125816196321</v>
       </c>
       <c r="G27">
-        <v>-4.548743690355574</v>
+        <v>-5.319246680256628</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.839494042930486</v>
       </c>
       <c r="E28">
-        <v>-29.51022862424821</v>
+        <v>-30.71033989915396</v>
       </c>
       <c r="F28">
-        <v>2.059416478363385</v>
+        <v>2.712953627332444</v>
       </c>
       <c r="G28">
-        <v>-4.649990104583104</v>
+        <v>-4.806618635137102</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.87217939886018</v>
       </c>
       <c r="E29">
-        <v>-28.55782261332502</v>
+        <v>-31.29219673168852</v>
       </c>
       <c r="F29">
-        <v>1.734476110736834</v>
+        <v>2.200538805839114</v>
       </c>
       <c r="G29">
-        <v>-4.116783708391469</v>
+        <v>-4.867780963975138</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.741066538635808</v>
       </c>
       <c r="E30">
-        <v>-28.1424755058155</v>
+        <v>-30.42261424612861</v>
       </c>
       <c r="F30">
-        <v>1.855517155633898</v>
+        <v>2.082141909691787</v>
       </c>
       <c r="G30">
-        <v>-4.68202956431217</v>
+        <v>-4.955411104399646</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.445047711094888</v>
       </c>
       <c r="E31">
-        <v>-28.67835247751317</v>
+        <v>-30.50438263704811</v>
       </c>
       <c r="F31">
-        <v>1.399121508122288</v>
+        <v>2.144948726172045</v>
       </c>
       <c r="G31">
-        <v>-4.3993586334415</v>
+        <v>-4.794747018833275</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.005198666113904</v>
       </c>
       <c r="E32">
-        <v>-28.29199213212675</v>
+        <v>-30.38531320572743</v>
       </c>
       <c r="F32">
-        <v>1.449572396422389</v>
+        <v>1.904985600194279</v>
       </c>
       <c r="G32">
-        <v>-4.054201155517086</v>
+        <v>-4.940937399301952</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-8.440986640300574</v>
       </c>
       <c r="E33">
-        <v>-28.86749325139154</v>
+        <v>-30.26297195193621</v>
       </c>
       <c r="F33">
-        <v>1.362015618681287</v>
+        <v>1.950731361646479</v>
       </c>
       <c r="G33">
-        <v>-3.723871611063068</v>
+        <v>-4.759330802654152</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.792223864850631</v>
       </c>
       <c r="E34">
-        <v>-27.96266791686694</v>
+        <v>-29.91145594980181</v>
       </c>
       <c r="F34">
-        <v>1.326944199581561</v>
+        <v>1.82631554795041</v>
       </c>
       <c r="G34">
-        <v>-4.292328696156862</v>
+        <v>-4.788543056492681</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.098794887089342</v>
       </c>
       <c r="E35">
-        <v>-26.61960856719806</v>
+        <v>-29.00146815490847</v>
       </c>
       <c r="F35">
-        <v>1.846242754192155</v>
+        <v>1.473595051103575</v>
       </c>
       <c r="G35">
-        <v>-4.030550618184533</v>
+        <v>-4.634221976179555</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.398512578790206</v>
       </c>
       <c r="E36">
-        <v>-26.38406452016309</v>
+        <v>-29.79285521554092</v>
       </c>
       <c r="F36">
-        <v>1.272474072643077</v>
+        <v>1.868658376111909</v>
       </c>
       <c r="G36">
-        <v>-3.999070640651603</v>
+        <v>-4.235450213246645</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.739654421749661</v>
       </c>
       <c r="E37">
-        <v>-26.39203010594258</v>
+        <v>-28.83722493112427</v>
       </c>
       <c r="F37">
-        <v>1.065937228103077</v>
+        <v>1.496988146558633</v>
       </c>
       <c r="G37">
-        <v>-3.371361411495933</v>
+        <v>-4.111850995537955</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.149636488249819</v>
       </c>
       <c r="E38">
-        <v>-26.89950901713815</v>
+        <v>-28.31299519457433</v>
       </c>
       <c r="F38">
-        <v>1.471320354215487</v>
+        <v>1.814968571266862</v>
       </c>
       <c r="G38">
-        <v>-3.774082655257194</v>
+        <v>-4.217682515337376</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-4.660735280246239</v>
       </c>
       <c r="E39">
-        <v>-25.98697169137849</v>
+        <v>-27.98610276985663</v>
       </c>
       <c r="F39">
-        <v>1.277426052977013</v>
+        <v>1.55431448430197</v>
       </c>
       <c r="G39">
-        <v>-2.948882831956301</v>
+        <v>-3.963806709567287</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-4.291845680763869</v>
       </c>
       <c r="E40">
-        <v>-25.19383663977908</v>
+        <v>-26.50348943669337</v>
       </c>
       <c r="F40">
-        <v>1.018453551839803</v>
+        <v>1.933552678447223</v>
       </c>
       <c r="G40">
-        <v>-2.847894640280833</v>
+        <v>-3.396485141593462</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-4.044322110922793</v>
       </c>
       <c r="E41">
-        <v>-24.78146926816661</v>
+        <v>-27.22475307731705</v>
       </c>
       <c r="F41">
-        <v>1.472115586922175</v>
+        <v>1.638481582630816</v>
       </c>
       <c r="G41">
-        <v>-3.673958515967476</v>
+        <v>-3.826091325679144</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.92756468236955</v>
       </c>
       <c r="E42">
-        <v>-24.25518360441718</v>
+        <v>-26.22995602120806</v>
       </c>
       <c r="F42">
-        <v>1.24828243101172</v>
+        <v>1.664626514597974</v>
       </c>
       <c r="G42">
-        <v>-3.16764699173688</v>
+        <v>-4.33908353080799</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.926344498614518</v>
       </c>
       <c r="E43">
-        <v>-23.51033114268754</v>
+        <v>-25.7857127210556</v>
       </c>
       <c r="F43">
-        <v>1.164027525738177</v>
+        <v>1.803513906820951</v>
       </c>
       <c r="G43">
-        <v>-3.597849074019632</v>
+        <v>-4.303564687717149</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-4.03002507718297</v>
       </c>
       <c r="E44">
-        <v>-23.50091191675159</v>
+        <v>-26.14273761182033</v>
       </c>
       <c r="F44">
-        <v>1.430942413533428</v>
+        <v>1.814161741416535</v>
       </c>
       <c r="G44">
-        <v>-4.439916126843111</v>
+        <v>-3.477831866584433</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-4.223665259165069</v>
       </c>
       <c r="E45">
-        <v>-21.80928233729029</v>
+        <v>-25.29679149634346</v>
       </c>
       <c r="F45">
-        <v>1.501832439130204</v>
+        <v>1.763197265326699</v>
       </c>
       <c r="G45">
-        <v>-4.550753191497911</v>
+        <v>-3.652708124150895</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-4.479077776863631</v>
       </c>
       <c r="E46">
-        <v>-22.2753347682637</v>
+        <v>-24.64098694750065</v>
       </c>
       <c r="F46">
-        <v>1.798808779973049</v>
+        <v>1.954240325964738</v>
       </c>
       <c r="G46">
-        <v>-4.052466429654508</v>
+        <v>-4.290603901930902</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-4.784587675869024</v>
       </c>
       <c r="E47">
-        <v>-21.39991734394491</v>
+        <v>-24.06446692158414</v>
       </c>
       <c r="F47">
-        <v>1.435491807309603</v>
+        <v>1.973102251726482</v>
       </c>
       <c r="G47">
-        <v>-4.193664507449964</v>
+        <v>-4.734279904558488</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.114442220146882</v>
       </c>
       <c r="E48">
-        <v>-21.04010291319145</v>
+        <v>-23.97295099036313</v>
       </c>
       <c r="F48">
-        <v>1.668789889164445</v>
+        <v>2.349119753409651</v>
       </c>
       <c r="G48">
-        <v>-4.257299813805834</v>
+        <v>-4.983176649837513</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-5.449329022856406</v>
       </c>
       <c r="E49">
-        <v>-21.52067363183345</v>
+        <v>-22.86200763290541</v>
       </c>
       <c r="F49">
-        <v>1.454287463679124</v>
+        <v>2.154971971745919</v>
       </c>
       <c r="G49">
-        <v>-4.460762632103902</v>
+        <v>-4.571258710568157</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.776385983093202</v>
       </c>
       <c r="E50">
-        <v>-20.73955262177638</v>
+        <v>-22.42910363166815</v>
       </c>
       <c r="F50">
-        <v>1.806989736443097</v>
+        <v>2.053584771847677</v>
       </c>
       <c r="G50">
-        <v>-4.272548186559717</v>
+        <v>-5.187523383794566</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.0744075623088</v>
       </c>
       <c r="E51">
-        <v>-19.91354084888128</v>
+        <v>-23.03210164510752</v>
       </c>
       <c r="F51">
-        <v>1.734993011996181</v>
+        <v>2.361589996291394</v>
       </c>
       <c r="G51">
-        <v>-4.267072544237763</v>
+        <v>-4.944204907749213</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.341238165606755</v>
       </c>
       <c r="E52">
-        <v>-20.57848385827156</v>
+        <v>-22.32854886632783</v>
       </c>
       <c r="F52">
-        <v>1.78177423270188</v>
+        <v>2.510127868756985</v>
       </c>
       <c r="G52">
-        <v>-4.566835821727691</v>
+        <v>-5.577412953045613</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.569394379154182</v>
       </c>
       <c r="E53">
-        <v>-19.043150030711</v>
+        <v>-21.76301038987992</v>
       </c>
       <c r="F53">
-        <v>1.928549339334314</v>
+        <v>2.386769051866888</v>
       </c>
       <c r="G53">
-        <v>-4.623485876995699</v>
+        <v>-4.875477982353943</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-6.756858100465355</v>
       </c>
       <c r="E54">
-        <v>-19.32251612071819</v>
+        <v>-20.65344821699454</v>
       </c>
       <c r="F54">
-        <v>1.531237825194781</v>
+        <v>2.479736725483077</v>
       </c>
       <c r="G54">
-        <v>-5.517170955867495</v>
+        <v>-5.269624913168492</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-6.912151334073487</v>
       </c>
       <c r="E55">
-        <v>-18.21140068124818</v>
+        <v>-20.29319905273634</v>
       </c>
       <c r="F55">
-        <v>1.822438788505308</v>
+        <v>2.567276935876123</v>
       </c>
       <c r="G55">
-        <v>-4.999855178264362</v>
+        <v>-5.503313012240106</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.033369757446915</v>
       </c>
       <c r="E56">
-        <v>-18.35393892911361</v>
+        <v>-20.0734322091441</v>
       </c>
       <c r="F56">
-        <v>1.998712058351432</v>
+        <v>2.697014181767776</v>
       </c>
       <c r="G56">
-        <v>-5.689858942832498</v>
+        <v>-6.141490186390952</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.134706138761151</v>
       </c>
       <c r="E57">
-        <v>-18.75495341638885</v>
+        <v>-18.84319526090232</v>
       </c>
       <c r="F57">
-        <v>2.357216216404613</v>
+        <v>2.671936187015424</v>
       </c>
       <c r="G57">
-        <v>-5.110169176723956</v>
+        <v>-5.548435747940372</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.221550726221087</v>
       </c>
       <c r="E58">
-        <v>-17.61364211223569</v>
+        <v>-19.7699701089421</v>
       </c>
       <c r="F58">
-        <v>2.096963059262675</v>
+        <v>2.667794350001426</v>
       </c>
       <c r="G58">
-        <v>-5.360429866765162</v>
+        <v>-5.65678328234964</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.2990692057594</v>
       </c>
       <c r="E59">
-        <v>-17.06221888926969</v>
+        <v>-18.48797270279264</v>
       </c>
       <c r="F59">
-        <v>2.16009128229522</v>
+        <v>2.7889861577658</v>
       </c>
       <c r="G59">
-        <v>-5.958241559155674</v>
+        <v>-6.521004505921923</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.379662051571945</v>
       </c>
       <c r="E60">
-        <v>-17.32974754822083</v>
+        <v>-18.49252381917035</v>
       </c>
       <c r="F60">
-        <v>2.268643860227679</v>
+        <v>2.511173268419318</v>
       </c>
       <c r="G60">
-        <v>-5.576999134853204</v>
+        <v>-6.51611151961488</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.458528366323526</v>
       </c>
       <c r="E61">
-        <v>-17.76792722167702</v>
+        <v>-18.52459900056668</v>
       </c>
       <c r="F61">
-        <v>2.262164370402981</v>
+        <v>2.465182310215889</v>
       </c>
       <c r="G61">
-        <v>-5.866244809164867</v>
+        <v>-7.270197514186688</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.545812168971967</v>
       </c>
       <c r="E62">
-        <v>-16.32093939353211</v>
+        <v>-17.67273416956179</v>
       </c>
       <c r="F62">
-        <v>2.135876446376585</v>
+        <v>2.797925898776811</v>
       </c>
       <c r="G62">
-        <v>-6.779882546001851</v>
+        <v>-6.697294366433653</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.639502061358453</v>
       </c>
       <c r="E63">
-        <v>-15.981403469385</v>
+        <v>-18.08813109028539</v>
       </c>
       <c r="F63">
-        <v>2.141583897781874</v>
+        <v>2.12831179525422</v>
       </c>
       <c r="G63">
-        <v>-6.724328281307341</v>
+        <v>-7.60755203627504</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-7.735303453532304</v>
       </c>
       <c r="E64">
-        <v>-15.4090269971855</v>
+        <v>-17.48479344129545</v>
       </c>
       <c r="F64">
-        <v>2.057058944735018</v>
+        <v>2.285005773167775</v>
       </c>
       <c r="G64">
-        <v>-6.504928496783221</v>
+        <v>-7.853866556033434</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.837334733029943</v>
       </c>
       <c r="E65">
-        <v>-15.85247781438662</v>
+        <v>-17.55676900717336</v>
       </c>
       <c r="F65">
-        <v>1.957812246205609</v>
+        <v>2.552642997338267</v>
       </c>
       <c r="G65">
-        <v>-6.968007606816475</v>
+        <v>-7.417463821955628</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.932136281540424</v>
       </c>
       <c r="E66">
-        <v>-15.32646385907766</v>
+        <v>-17.99464074439703</v>
       </c>
       <c r="F66">
-        <v>2.034063465633304</v>
+        <v>2.41556641625781</v>
       </c>
       <c r="G66">
-        <v>-6.688905444037139</v>
+        <v>-8.101386114368124</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-8.023209835341756</v>
       </c>
       <c r="E67">
-        <v>-16.39105828506688</v>
+        <v>-17.58365908583091</v>
       </c>
       <c r="F67">
-        <v>1.947167725079635</v>
+        <v>2.237722561815979</v>
       </c>
       <c r="G67">
-        <v>-6.656707078122188</v>
+        <v>-8.051443224362679</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-8.103920278234343</v>
       </c>
       <c r="E68">
-        <v>-15.71644698367021</v>
+        <v>-18.2636592712967</v>
       </c>
       <c r="F68">
-        <v>1.564236669052702</v>
+        <v>2.421530661557967</v>
       </c>
       <c r="G68">
-        <v>-6.825879265724485</v>
+        <v>-8.37725387415559</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-8.166340549284298</v>
       </c>
       <c r="E69">
-        <v>-15.37716465406753</v>
+        <v>-16.36966577385464</v>
       </c>
       <c r="F69">
-        <v>1.999114644909192</v>
+        <v>2.719792628609957</v>
       </c>
       <c r="G69">
-        <v>-7.132247081565258</v>
+        <v>-8.400440935112647</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-8.21381564822766</v>
       </c>
       <c r="E70">
-        <v>-16.22356814541918</v>
+        <v>-17.15813196875215</v>
       </c>
       <c r="F70">
-        <v>1.982436295621227</v>
+        <v>2.072002692681521</v>
       </c>
       <c r="G70">
-        <v>-6.998851959605864</v>
+        <v>-8.622379908065387</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-8.23409722255713</v>
       </c>
       <c r="E71">
-        <v>-15.55788246629164</v>
+        <v>-16.71541023586627</v>
       </c>
       <c r="F71">
-        <v>2.030478291513987</v>
+        <v>2.037960105896072</v>
       </c>
       <c r="G71">
-        <v>-7.247917542707393</v>
+        <v>-8.137030758189455</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-8.232165013409421</v>
       </c>
       <c r="E72">
-        <v>-15.67488464922782</v>
+        <v>-16.09514967950966</v>
       </c>
       <c r="F72">
-        <v>1.924975762358637</v>
+        <v>1.723216940997983</v>
       </c>
       <c r="G72">
-        <v>-7.149822767833249</v>
+        <v>-8.062857985382085</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-8.205760250538509</v>
       </c>
       <c r="E73">
-        <v>-15.2701658702143</v>
+        <v>-17.68832570557019</v>
       </c>
       <c r="F73">
-        <v>1.982249084588194</v>
+        <v>2.310514518969582</v>
       </c>
       <c r="G73">
-        <v>-7.564816203908588</v>
+        <v>-8.770361293670808</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-8.151480758332564</v>
       </c>
       <c r="E74">
-        <v>-15.88143740566568</v>
+        <v>-16.99128487241354</v>
       </c>
       <c r="F74">
-        <v>1.710811310773658</v>
+        <v>2.082860932597417</v>
       </c>
       <c r="G74">
-        <v>-7.012792666871736</v>
+        <v>-8.576270629794418</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-8.079346012763313</v>
       </c>
       <c r="E75">
-        <v>-15.40198069162957</v>
+        <v>-16.98626279473904</v>
       </c>
       <c r="F75">
-        <v>2.137407269336959</v>
+        <v>1.847125793843539</v>
       </c>
       <c r="G75">
-        <v>-6.727959949763921</v>
+        <v>-8.02799794085356</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.98443574328952</v>
       </c>
       <c r="E76">
-        <v>-15.72931690680001</v>
+        <v>-16.49370520539874</v>
       </c>
       <c r="F76">
-        <v>1.495291650117699</v>
+        <v>1.651223530020678</v>
       </c>
       <c r="G76">
-        <v>-6.923083503848565</v>
+        <v>-7.955794942642055</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.878035158960472</v>
       </c>
       <c r="E77">
-        <v>-16.42256287873824</v>
+        <v>-17.4253119352047</v>
       </c>
       <c r="F77">
-        <v>1.575025326106763</v>
+        <v>1.444105171563912</v>
       </c>
       <c r="G77">
-        <v>-6.095606025216653</v>
+        <v>-7.577416140231055</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.765257792200962</v>
       </c>
       <c r="E78">
-        <v>-16.52273272378791</v>
+        <v>-17.36712557268014</v>
       </c>
       <c r="F78">
-        <v>1.657828931690602</v>
+        <v>1.551413541657366</v>
       </c>
       <c r="G78">
-        <v>-5.973092666444844</v>
+        <v>-7.266340728633438</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-7.646511950835825</v>
       </c>
       <c r="E79">
-        <v>-16.20794491009272</v>
+        <v>-17.56956194624503</v>
       </c>
       <c r="F79">
-        <v>1.577217186254571</v>
+        <v>1.481111656916577</v>
       </c>
       <c r="G79">
-        <v>-6.042531359131058</v>
+        <v>-7.627921822978176</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-7.535977652368063</v>
       </c>
       <c r="E80">
-        <v>-16.45077527180602</v>
+        <v>-18.34778020446318</v>
       </c>
       <c r="F80">
-        <v>1.04983542252746</v>
+        <v>1.707665171377825</v>
       </c>
       <c r="G80">
-        <v>-6.608720720530451</v>
+        <v>-7.036234639835315</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-7.430289399019031</v>
       </c>
       <c r="E81">
-        <v>-17.25679836043127</v>
+        <v>-18.23854435445016</v>
       </c>
       <c r="F81">
-        <v>1.136981330036773</v>
+        <v>1.807488413619583</v>
       </c>
       <c r="G81">
-        <v>-6.216781923590596</v>
+        <v>-7.201467278245879</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-7.339704932077354</v>
       </c>
       <c r="E82">
-        <v>-18.87790601417111</v>
+        <v>-20.49834345375782</v>
       </c>
       <c r="F82">
-        <v>1.33993962739668</v>
+        <v>1.201522747858494</v>
       </c>
       <c r="G82">
-        <v>-5.941344534723234</v>
+        <v>-7.174224799003216</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-7.269569368239529</v>
       </c>
       <c r="E83">
-        <v>-17.87126247005805</v>
+        <v>-20.39123145805439</v>
       </c>
       <c r="F83">
-        <v>0.8079985294845609</v>
+        <v>1.201666883786581</v>
       </c>
       <c r="G83">
-        <v>-6.386785058123251</v>
+        <v>-6.866032872570305</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-7.216984352698079</v>
       </c>
       <c r="E84">
-        <v>-18.85276392648053</v>
+        <v>-20.76113532889694</v>
       </c>
       <c r="F84">
-        <v>1.405934001642911</v>
+        <v>1.249018021265407</v>
       </c>
       <c r="G84">
-        <v>-5.271839668134264</v>
+        <v>-6.986619493838258</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-7.196610688256574</v>
       </c>
       <c r="E85">
-        <v>-20.5215926393132</v>
+        <v>-22.92492625076798</v>
       </c>
       <c r="F85">
-        <v>0.7476403670469777</v>
+        <v>0.9842336944301556</v>
       </c>
       <c r="G85">
-        <v>-5.775827189396292</v>
+        <v>-6.225478726722262</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-7.20481080288467</v>
       </c>
       <c r="E86">
-        <v>-22.02348821480112</v>
+        <v>-23.33597583644422</v>
       </c>
       <c r="F86">
-        <v>1.020691800562167</v>
+        <v>0.6489652420255005</v>
       </c>
       <c r="G86">
-        <v>-4.962859831863006</v>
+        <v>-5.447725642090203</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-7.250492610863345</v>
       </c>
       <c r="E87">
-        <v>-22.48802360698195</v>
+        <v>-25.14986062869059</v>
       </c>
       <c r="F87">
-        <v>0.5001589785214029</v>
+        <v>1.076112893279066</v>
       </c>
       <c r="G87">
-        <v>-5.115502465587722</v>
+        <v>-6.305252942582079</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-7.341659476353473</v>
       </c>
       <c r="E88">
-        <v>-24.49776490006007</v>
+        <v>-25.12969986240844</v>
       </c>
       <c r="F88">
-        <v>0.7374299104400709</v>
+        <v>0.5973529826266746</v>
       </c>
       <c r="G88">
-        <v>-4.255333349755507</v>
+        <v>-5.610955400449509</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-7.471923450452701</v>
       </c>
       <c r="E89">
-        <v>-25.86842982727971</v>
+        <v>-27.28366852415684</v>
       </c>
       <c r="F89">
-        <v>0.3104081710317314</v>
+        <v>0.3814970048051793</v>
       </c>
       <c r="G89">
-        <v>-3.823307156880617</v>
+        <v>-5.144320764507078</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-7.656341721573705</v>
       </c>
       <c r="E90">
-        <v>-27.65032547913589</v>
+        <v>-28.60873624659325</v>
       </c>
       <c r="F90">
-        <v>0.03051939297383443</v>
+        <v>0.371619551894198</v>
       </c>
       <c r="G90">
-        <v>-3.976105386245679</v>
+        <v>-4.829348840809739</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-7.888941386598296</v>
       </c>
       <c r="E91">
-        <v>-28.97064736081226</v>
+        <v>-29.85151480359928</v>
       </c>
       <c r="F91">
-        <v>-0.2105338645060161</v>
+        <v>-0.2196616449174638</v>
       </c>
       <c r="G91">
-        <v>-4.470555225809067</v>
+        <v>-5.322908143623062</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-8.171730326207125</v>
       </c>
       <c r="E92">
-        <v>-30.73024027818067</v>
+        <v>-31.796673264617</v>
       </c>
       <c r="F92">
-        <v>-0.4676938977659002</v>
+        <v>-0.09305645617579582</v>
       </c>
       <c r="G92">
-        <v>-4.333776726308538</v>
+        <v>-5.492772235243066</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-8.509258730958921</v>
       </c>
       <c r="E93">
-        <v>-31.89535097748114</v>
+        <v>-33.47607143578357</v>
       </c>
       <c r="F93">
-        <v>-0.1419168790625218</v>
+        <v>-0.2124134301429682</v>
       </c>
       <c r="G93">
-        <v>-3.635708472806737</v>
+        <v>-4.684141692366225</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-8.885054760088652</v>
       </c>
       <c r="E94">
-        <v>-34.37490107072202</v>
+        <v>-34.79069649715829</v>
       </c>
       <c r="F94">
-        <v>-0.5607568336334107</v>
+        <v>-0.5217630948814296</v>
       </c>
       <c r="G94">
-        <v>-3.911149172219639</v>
+        <v>-4.654810258888283</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.30629282993908</v>
       </c>
       <c r="E95">
-        <v>-36.63352276678769</v>
+        <v>-37.72853495268642</v>
       </c>
       <c r="F95">
-        <v>-1.012719887172641</v>
+        <v>-0.991695922489589</v>
       </c>
       <c r="G95">
-        <v>-4.101330081814151</v>
+        <v>-5.450652164346919</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.761304334075039</v>
       </c>
       <c r="E96">
-        <v>-38.48790570208465</v>
+        <v>-40.21533739705059</v>
       </c>
       <c r="F96">
-        <v>-1.582146266796243</v>
+        <v>-0.8625401905147013</v>
       </c>
       <c r="G96">
-        <v>-3.590459936375978</v>
+        <v>-4.952372023594595</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-10.23653184676387</v>
       </c>
       <c r="E97">
-        <v>-40.70543149653071</v>
+        <v>-41.96467784926563</v>
       </c>
       <c r="F97">
-        <v>-1.748166833297917</v>
+        <v>-1.428260454378179</v>
       </c>
       <c r="G97">
-        <v>-3.868549072220298</v>
+        <v>-4.665668848257092</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.73671988884184</v>
       </c>
       <c r="E98">
-        <v>-43.68354619988306</v>
+        <v>-44.75611074012578</v>
       </c>
       <c r="F98">
-        <v>-1.819688903223029</v>
+        <v>-1.308258182204226</v>
       </c>
       <c r="G98">
-        <v>-4.134455400480098</v>
+        <v>-4.684039065454508</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-11.22410213498752</v>
       </c>
       <c r="E99">
-        <v>-46.04881798730337</v>
+        <v>-46.10173547032</v>
       </c>
       <c r="F99">
-        <v>-2.606844199365857</v>
+        <v>-1.943320252988647</v>
       </c>
       <c r="G99">
-        <v>-4.281569423154231</v>
+        <v>-5.344691533271466</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-11.71880668948921</v>
       </c>
       <c r="E100">
-        <v>-48.54827298804496</v>
+        <v>-49.06048189034155</v>
       </c>
       <c r="F100">
-        <v>-2.606748937114535</v>
+        <v>-2.009456278060757</v>
       </c>
       <c r="G100">
-        <v>-4.967865376718384</v>
+        <v>-5.074574191085712</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-12.17021005493441</v>
       </c>
       <c r="E101">
-        <v>-51.10528036495004</v>
+        <v>-51.42684730423471</v>
       </c>
       <c r="F101">
-        <v>-2.655780003686238</v>
+        <v>-2.519465520616357</v>
       </c>
       <c r="G101">
-        <v>-4.466764651166601</v>
+        <v>-5.50801729745141</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-12.61778741972458</v>
       </c>
       <c r="E102">
-        <v>-52.55965753055698</v>
+        <v>-53.64260020110677</v>
       </c>
       <c r="F102">
-        <v>-3.495883715848607</v>
+        <v>-2.85914254433871</v>
       </c>
       <c r="G102">
-        <v>-5.530154915472517</v>
+        <v>-6.154394692903031</v>
       </c>
     </row>
   </sheetData>
